--- a/DrawOrder.xlsx
+++ b/DrawOrder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MyGame\Ghost\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9FFF4A9-29E1-4D89-829D-B706DAD6EA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93305B4-0F50-4781-A2C1-3009AB101934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="1810" windowWidth="13820" windowHeight="12760" xr2:uid="{5D58F740-12BF-407C-9066-BF6783D4553B}"/>
+    <workbookView xWindow="160" yWindow="0" windowWidth="9330" windowHeight="14410" xr2:uid="{5D58F740-12BF-407C-9066-BF6783D4553B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>DrawingOrder</t>
     <phoneticPr fontId="1"/>
@@ -50,11 +50,79 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>PlayerCircle</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>StageObjectSquare</t>
+    <t>Battery_StageMenuCC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CandleCC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Brock_StageMenuSC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Canlde_mBarSC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DoorSC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Door_StageMenuCC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Escapee_CreateStage_mBarSC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FlashlightTC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ghost_CreateStage_mBarSC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HandCC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Patrol_StageMenuCC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Patrol_mBarSC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Patrol_mPluMinusCC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PlayerCC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StageObjectCC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StageObjectSC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>StageObjectLightTC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TreasureChest_StageMenuSC</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TreasureChest_StageMenuCC</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -439,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A744673-07A8-4429-90E3-009A390ACF14}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="13.08203125" customWidth="1"/>
@@ -463,18 +531,208 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>-1</v>
+      </c>
+      <c r="D2">
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>-1</v>
+      </c>
+      <c r="D3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C4">
+        <v>200</v>
+      </c>
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="D3">
-        <v>100</v>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>-1</v>
+      </c>
+      <c r="D5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>150</v>
+      </c>
+      <c r="D6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>-1</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8">
+        <v>-1</v>
+      </c>
+      <c r="D8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>200</v>
+      </c>
+      <c r="D9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>-1</v>
+      </c>
+      <c r="D10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>-1</v>
+      </c>
+      <c r="D11">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>-1</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13">
+        <v>-1</v>
+      </c>
+      <c r="D13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14">
+        <v>-1</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>170</v>
+      </c>
+      <c r="D15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16">
+        <v>50</v>
+      </c>
+      <c r="D16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17">
+        <v>-1</v>
+      </c>
+      <c r="D17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18">
+        <v>200</v>
+      </c>
+      <c r="D18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>-1</v>
+      </c>
+      <c r="D19">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20">
+        <v>-1</v>
+      </c>
+      <c r="D20">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
